--- a/Excel Daily Challenges.xlsx
+++ b/Excel Daily Challenges.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D516F96-37C1-4615-9020-94DAA97550B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F2E33D-AAF6-435E-BB77-25D9D3F61D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" firstSheet="25" activeTab="25" xr2:uid="{0ACB132C-7219-4B66-ACBB-64BA10C47BDC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{0ACB132C-7219-4B66-ACBB-64BA10C47BDC}"/>
   </bookViews>
   <sheets>
     <sheet name="More --&gt;" sheetId="19" state="hidden" r:id="rId1"/>
-    <sheet name="Daily Challenge 1 - Cleaning" sheetId="22" r:id="rId2"/>
+    <sheet name="Daily Challenge 1 - Cleaning" sheetId="32" r:id="rId2"/>
     <sheet name="Daily Challenge 2 - IF" sheetId="17" r:id="rId3"/>
     <sheet name="Daily Challenge 3 - SUMIFS" sheetId="18" r:id="rId4"/>
     <sheet name="Daily Challenge 4 - SumProduct" sheetId="21" r:id="rId5"/>
@@ -41,10 +41,11 @@
     <externalReference r:id="rId29"/>
     <externalReference r:id="rId30"/>
     <externalReference r:id="rId31"/>
+    <externalReference r:id="rId32"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Aggregate!$A$6:$D$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Challenge 1 - Cleaning'!$B$6:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Challenge 1 - Cleaning'!$B$6:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Daily Challenge 2 - IF'!$A$6:$D$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Daily Challenge 3 - SUMIFS'!$A$7:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Daily Challenge 9 - IS Number'!$A$11:$D$11</definedName>
@@ -53,7 +54,8 @@
     <definedName name="AnswerProductTable">'[1]V Exact (an)'!$A$12:$D$19</definedName>
     <definedName name="applist">INDEX(('Index Match '!$A$37:$A$51,'Index Match '!$B$37:$B$51,'Index Match '!$C$37:$C$51),,,'Index Match '!$I$36)</definedName>
     <definedName name="Flag">INDIRECT([2]Report!$C$2)</definedName>
-    <definedName name="mylist">INDEX(([3]!TableProd[Productivity],[3]!TableGame[Games],[3]!TableUtility[Utility]),,,MATCH([3]Table!$F$4,[3]Table!$A$4:$C$4,0))</definedName>
+    <definedName name="mylist" localSheetId="1">INDEX(([3]!TableProd[Productivity],[3]!TableGame[Games],[3]!TableUtility[Utility]),,,MATCH([3]Table!$F$4,[3]Table!$A$4:$C$4,0))</definedName>
+    <definedName name="mylist">INDEX(([4]!TableProd[Productivity],[4]!TableGame[Games],[4]!TableUtility[Utility]),,,MATCH([4]Table!$F$4,[4]Table!$A$4:$C$4,0))</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -67,8 +69,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="480">
   <si>
     <t>Free Tutorials</t>
   </si>
@@ -1596,28 +1596,31 @@
   <si>
     <t>Overnight borrowing</t>
   </si>
+  <si>
+    <t>NaN</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="16">
-    <numFmt numFmtId="8" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
-    <numFmt numFmtId="171" formatCode="#,##0;[Red]\(#,##0\)"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="&quot;$&quot;\ #,##0;[Red]&quot;$&quot;\ \-#,##0"/>
-    <numFmt numFmtId="174" formatCode="[Blue]\ &quot;KES&quot;\ #,##0.00;[Red]\ &quot;KES&quot;\ \(#,##0.00\)"/>
-    <numFmt numFmtId="175" formatCode="0.0%"/>
-    <numFmt numFmtId="176" formatCode="[Blue]\ &quot;KES&quot;\ #,##0.00;[Red]\ &quot;KES&quot;\ \(\(#,##0.00\)\)"/>
-    <numFmt numFmtId="177" formatCode="0.0%;\(0.0%\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;£&quot;#,##0.00;[Red]\-&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="172" formatCode="#,##0;[Red]\(#,##0\)"/>
+    <numFmt numFmtId="173" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="174" formatCode="&quot;$&quot;\ #,##0;[Red]&quot;$&quot;\ \-#,##0"/>
+    <numFmt numFmtId="175" formatCode="[Blue]\ &quot;KES&quot;\ #,##0.00;[Red]\ &quot;KES&quot;\ \(#,##0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="[Blue]\ &quot;KES&quot;\ #,##0.00;[Red]\ &quot;KES&quot;\ \(\(#,##0.00\)\)"/>
+    <numFmt numFmtId="178" formatCode="0.0%;\(0.0%\)"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -2583,8 +2586,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
@@ -2624,16 +2627,16 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2642,37 +2645,37 @@
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="6" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="7" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="10" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="10" fillId="10" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="8" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="11"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2706,9 +2709,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="5" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="5" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2732,8 +2735,8 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="19" borderId="11" xfId="8" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="19" borderId="11" xfId="8" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" wrapText="1"/>
     </xf>
@@ -2741,8 +2744,8 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="19" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="11" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2758,10 +2761,10 @@
     <xf numFmtId="14" fontId="21" fillId="0" borderId="11" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="11" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="21" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="11" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2770,7 +2773,7 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="9" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="9" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
@@ -2790,62 +2793,62 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="23" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="23" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="23" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="23" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="25" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="23" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="23" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="25" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="23" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="23" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="25" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="23" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="23" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="25" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="23" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="25" fillId="23" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="25" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="23" fillId="23" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="23" fillId="23" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="25" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="25" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="24" fillId="22" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2898,7 +2901,7 @@
     <cellStyle name="Percent" xfId="9" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="12" xr:uid="{ECCEC94D-8720-4B08-A6AD-07F7FD42CF90}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <condense val="0"/>
@@ -2908,6 +2911,28 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4472C4"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4137,25 +4162,15 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>216647</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>119530</xdr:rowOff>
-    </xdr:to>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="508000" y="1"/>
+    <xdr:ext cx="6432176" cy="896470"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{763F9BC8-8A44-4956-8C28-7F6DD6E6365F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{443BD28D-6D1F-4A02-8636-6D5E5A42B466}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4286,7 +4301,7 @@
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:absoluteAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5459,10 +5474,29 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Notes"/>
+      <sheetName val="OFFSET"/>
+      <sheetName val="Table"/>
+      <sheetName val="Excel_Dependent_Dropdown_Expand"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5500,7 +5534,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5606,7 +5640,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5748,7 +5782,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7677,17 +7711,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23C73FB-CD98-48E5-BE26-E119DF8D3E8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9D0D85-8CD5-422A-BDDE-3C83A0A8344B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="B6:I47"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="7.26953125" style="59" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.54296875" style="120" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" style="120" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" style="120" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.1796875" style="59" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" style="59" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" style="120" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" style="120" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" style="120" customWidth="1"/>
+    <col min="6" max="7" width="13" style="59" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" style="59" customWidth="1"/>
     <col min="9" max="9" width="14.1796875" style="59" customWidth="1"/>
     <col min="10" max="16384" width="11.54296875" style="59"/>
   </cols>
@@ -7718,7 +7753,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="24.5">
+    <row r="7" spans="2:9">
       <c r="B7" s="121">
         <v>45076</v>
       </c>
@@ -7740,7 +7775,10 @@
       <c r="H7" s="122">
         <v>598</v>
       </c>
-      <c r="I7" s="123"/>
+      <c r="I7" s="123">
+        <f t="shared" ref="I7:I37" si="0">H7/G7</f>
+        <v>0.13288888888888889</v>
+      </c>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="121">
@@ -7764,9 +7802,12 @@
       <c r="H8" s="122">
         <v>1045</v>
       </c>
-      <c r="I8" s="123"/>
-    </row>
-    <row r="9" spans="2:9" ht="24.5">
+      <c r="I8" s="123">
+        <f t="shared" si="0"/>
+        <v>0.27500000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
       <c r="B9" s="121">
         <v>45076</v>
       </c>
@@ -7779,16 +7820,21 @@
       <c r="E9" s="119" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="119"/>
+      <c r="F9" s="119" t="s">
+        <v>479</v>
+      </c>
       <c r="G9" s="122">
         <v>3712.5</v>
       </c>
       <c r="H9" s="122">
         <v>1009</v>
       </c>
-      <c r="I9" s="123"/>
-    </row>
-    <row r="10" spans="2:9" ht="48.5">
+      <c r="I9" s="123">
+        <f t="shared" si="0"/>
+        <v>0.2717845117845118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
       <c r="B10" s="121">
         <v>45076</v>
       </c>
@@ -7801,7 +7847,9 @@
       <c r="E10" s="119" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="119"/>
+      <c r="F10" s="119" t="s">
+        <v>479</v>
+      </c>
       <c r="G10" s="122">
         <f>G9*1.5</f>
         <v>5568.75</v>
@@ -7809,9 +7857,12 @@
       <c r="H10" s="122">
         <v>779</v>
       </c>
-      <c r="I10" s="123"/>
-    </row>
-    <row r="11" spans="2:9" ht="60.5">
+      <c r="I10" s="123">
+        <f t="shared" si="0"/>
+        <v>0.13988776655443322</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
       <c r="B11" s="121">
         <v>45076</v>
       </c>
@@ -7833,9 +7884,12 @@
       <c r="H11" s="122">
         <v>684</v>
       </c>
-      <c r="I11" s="123"/>
-    </row>
-    <row r="12" spans="2:9" ht="36.5">
+      <c r="I11" s="123">
+        <f t="shared" si="0"/>
+        <v>0.1368</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" hidden="1">
       <c r="B12" s="121">
         <v>45077</v>
       </c>
@@ -7857,9 +7911,12 @@
       <c r="H12" s="122">
         <v>544</v>
       </c>
-      <c r="I12" s="123"/>
-    </row>
-    <row r="13" spans="2:9" ht="24.5">
+      <c r="I12" s="123">
+        <f t="shared" si="0"/>
+        <v>8.9180327868852466E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
       <c r="B13" s="121">
         <v>45077</v>
       </c>
@@ -7881,9 +7938,12 @@
       <c r="H13" s="122">
         <v>670</v>
       </c>
-      <c r="I13" s="123"/>
-    </row>
-    <row r="14" spans="2:9" ht="24.5">
+      <c r="I13" s="123">
+        <f t="shared" si="0"/>
+        <v>0.14486486486486486</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
       <c r="B14" s="121">
         <v>45077</v>
       </c>
@@ -7905,9 +7965,12 @@
       <c r="H14" s="122">
         <v>2045</v>
       </c>
-      <c r="I14" s="123"/>
-    </row>
-    <row r="15" spans="2:9" ht="48.5">
+      <c r="I14" s="123">
+        <f t="shared" si="0"/>
+        <v>0.53815789473684206</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
       <c r="B15" s="121">
         <v>45077</v>
       </c>
@@ -7929,9 +7992,12 @@
       <c r="H15" s="122">
         <v>1564</v>
       </c>
-      <c r="I15" s="123"/>
-    </row>
-    <row r="16" spans="2:9" ht="24.5">
+      <c r="I15" s="123">
+        <f t="shared" si="0"/>
+        <v>0.43444444444444447</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
       <c r="B16" s="121">
         <v>45077</v>
       </c>
@@ -7953,9 +8019,12 @@
       <c r="H16" s="122">
         <v>1220</v>
       </c>
-      <c r="I16" s="123"/>
-    </row>
-    <row r="17" spans="2:9" ht="36.5">
+      <c r="I16" s="123">
+        <f t="shared" si="0"/>
+        <v>0.23921568627450981</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="121">
         <v>45077</v>
       </c>
@@ -7977,9 +8046,12 @@
       <c r="H17" s="122">
         <v>1435</v>
       </c>
-      <c r="I17" s="123"/>
-    </row>
-    <row r="18" spans="2:9" ht="60.5">
+      <c r="I17" s="123">
+        <f t="shared" si="0"/>
+        <v>0.30210526315789471</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
       <c r="B18" s="121">
         <v>45077</v>
       </c>
@@ -8001,9 +8073,12 @@
       <c r="H18" s="122">
         <v>998</v>
       </c>
-      <c r="I18" s="123"/>
-    </row>
-    <row r="19" spans="2:9" ht="48.5">
+      <c r="I18" s="123">
+        <f t="shared" si="0"/>
+        <v>0.16633333333333333</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="121">
         <v>45077</v>
       </c>
@@ -8025,9 +8100,12 @@
       <c r="H19" s="122">
         <v>780</v>
       </c>
-      <c r="I19" s="123"/>
-    </row>
-    <row r="20" spans="2:9" ht="48.5">
+      <c r="I19" s="123">
+        <f t="shared" si="0"/>
+        <v>0.17333333333333334</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="121">
         <v>45078</v>
       </c>
@@ -8050,9 +8128,12 @@
       <c r="H20" s="122">
         <v>1044</v>
       </c>
-      <c r="I20" s="123"/>
-    </row>
-    <row r="21" spans="2:9" ht="48.5">
+      <c r="I20" s="123">
+        <f t="shared" si="0"/>
+        <v>0.15466666666666667</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" s="121">
         <v>45078</v>
       </c>
@@ -8074,9 +8155,12 @@
       <c r="H21" s="122">
         <v>1222</v>
       </c>
-      <c r="I21" s="123"/>
-    </row>
-    <row r="22" spans="2:9" ht="36.5">
+      <c r="I21" s="123">
+        <f t="shared" si="0"/>
+        <v>0.32915824915824915</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="121">
         <v>45078</v>
       </c>
@@ -8098,9 +8182,12 @@
       <c r="H22" s="122">
         <v>1065</v>
       </c>
-      <c r="I22" s="123"/>
-    </row>
-    <row r="23" spans="2:9" ht="36.5">
+      <c r="I22" s="123">
+        <f t="shared" si="0"/>
+        <v>0.21515151515151515</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="121">
         <v>45078</v>
       </c>
@@ -8122,9 +8209,12 @@
       <c r="H23" s="122">
         <v>810</v>
       </c>
-      <c r="I23" s="123"/>
-    </row>
-    <row r="24" spans="2:9" ht="36.5">
+      <c r="I23" s="123">
+        <f t="shared" si="0"/>
+        <v>0.17052631578947369</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
       <c r="B24" s="121">
         <v>45078</v>
       </c>
@@ -8146,9 +8236,12 @@
       <c r="H24" s="122">
         <v>933</v>
       </c>
-      <c r="I24" s="123"/>
-    </row>
-    <row r="25" spans="2:9" ht="60.5">
+      <c r="I24" s="123">
+        <f t="shared" si="0"/>
+        <v>0.12745901639344262</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="121">
         <v>45077</v>
       </c>
@@ -8170,9 +8263,12 @@
       <c r="H25" s="122">
         <v>998</v>
       </c>
-      <c r="I25" s="123"/>
-    </row>
-    <row r="26" spans="2:9" ht="48.5">
+      <c r="I25" s="123">
+        <f t="shared" si="0"/>
+        <v>0.16633333333333333</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
       <c r="B26" s="121">
         <v>45077</v>
       </c>
@@ -8194,7 +8290,10 @@
       <c r="H26" s="122">
         <v>780</v>
       </c>
-      <c r="I26" s="123"/>
+      <c r="I26" s="123">
+        <f t="shared" si="0"/>
+        <v>0.17333333333333334</v>
+      </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="121">
@@ -8218,9 +8317,12 @@
       <c r="H27" s="122">
         <v>655</v>
       </c>
-      <c r="I27" s="123"/>
-    </row>
-    <row r="28" spans="2:9" ht="36.5">
+      <c r="I27" s="123">
+        <f t="shared" si="0"/>
+        <v>0.12874692874692875</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
       <c r="B28" s="121">
         <v>45078</v>
       </c>
@@ -8242,9 +8344,12 @@
       <c r="H28" s="122">
         <v>722</v>
       </c>
-      <c r="I28" s="123"/>
-    </row>
-    <row r="29" spans="2:9" ht="36.5">
+      <c r="I28" s="123">
+        <f t="shared" si="0"/>
+        <v>0.16044444444444445</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="B29" s="121">
         <v>45078</v>
       </c>
@@ -8266,9 +8371,12 @@
       <c r="H29" s="122">
         <v>901</v>
       </c>
-      <c r="I29" s="123"/>
-    </row>
-    <row r="30" spans="2:9" ht="48.5">
+      <c r="I29" s="123">
+        <f t="shared" si="0"/>
+        <v>0.21199999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="B30" s="121">
         <v>45079</v>
       </c>
@@ -8290,9 +8398,12 @@
       <c r="H30" s="122">
         <v>1349</v>
       </c>
-      <c r="I30" s="123"/>
-    </row>
-    <row r="31" spans="2:9" ht="36.5">
+      <c r="I30" s="123">
+        <f t="shared" si="0"/>
+        <v>0.25695238095238093</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
       <c r="B31" s="121">
         <v>45079</v>
       </c>
@@ -8314,9 +8425,12 @@
       <c r="H31" s="122">
         <v>1288</v>
       </c>
-      <c r="I31" s="123"/>
-    </row>
-    <row r="32" spans="2:9" ht="36.5">
+      <c r="I31" s="123">
+        <f t="shared" si="0"/>
+        <v>0.19815384615384615</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="B32" s="121">
         <v>45079</v>
       </c>
@@ -8338,9 +8452,12 @@
       <c r="H32" s="122">
         <v>1664</v>
       </c>
-      <c r="I32" s="123"/>
-    </row>
-    <row r="33" spans="2:9" ht="36.5">
+      <c r="I32" s="123">
+        <f t="shared" si="0"/>
+        <v>0.22186666666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
       <c r="B33" s="121">
         <v>45079</v>
       </c>
@@ -8362,9 +8479,12 @@
       <c r="H33" s="122">
         <v>1320</v>
       </c>
-      <c r="I33" s="123"/>
-    </row>
-    <row r="34" spans="2:9" ht="36.5">
+      <c r="I33" s="123">
+        <f t="shared" si="0"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
       <c r="B34" s="121">
         <v>45079</v>
       </c>
@@ -8386,9 +8506,12 @@
       <c r="H34" s="122">
         <v>1001</v>
       </c>
-      <c r="I34" s="123"/>
-    </row>
-    <row r="35" spans="2:9" ht="36.5">
+      <c r="I34" s="123">
+        <f t="shared" si="0"/>
+        <v>0.21643243243243243</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
       <c r="B35" s="121">
         <v>45079</v>
       </c>
@@ -8410,9 +8533,12 @@
       <c r="H35" s="122">
         <v>960</v>
       </c>
-      <c r="I35" s="123"/>
-    </row>
-    <row r="36" spans="2:9" ht="48.5">
+      <c r="I35" s="123">
+        <f t="shared" si="0"/>
+        <v>0.21333333333333335</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" hidden="1">
       <c r="B36" s="121">
         <v>45079</v>
       </c>
@@ -8434,9 +8560,12 @@
       <c r="H36" s="122">
         <v>540</v>
       </c>
-      <c r="I36" s="123"/>
-    </row>
-    <row r="37" spans="2:9" ht="60.5">
+      <c r="I36" s="123">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
       <c r="B37" s="121">
         <v>45076</v>
       </c>
@@ -8458,7 +8587,10 @@
       <c r="H37" s="122">
         <v>684</v>
       </c>
-      <c r="I37" s="123"/>
+      <c r="I37" s="123">
+        <f t="shared" si="0"/>
+        <v>0.1368</v>
+      </c>
     </row>
     <row r="38" spans="2:9">
       <c r="G38" s="60"/>
@@ -8491,8 +8623,24 @@
       <c r="G47" s="86"/>
     </row>
   </sheetData>
+  <autoFilter ref="B6:I37" xr:uid="{C23C73FB-CD98-48E5-BE26-E119DF8D3E8A}">
+    <filterColumn colId="7">
+      <colorFilter dxfId="3"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="I7:I37">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L34">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
